--- a/data/topics_codebook.xlsx
+++ b/data/topics_codebook.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="647" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CF1222-91BE-4C1B-A559-B8CAEB1FCDA7}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="28785" yWindow="2730" windowWidth="11670" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>

--- a/data/topics_codebook.xlsx
+++ b/data/topics_codebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="647" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{16CF1222-91BE-4C1B-A559-B8CAEB1FCDA7}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E63C9749-D00C-4EFE-ADA8-2469FDEB6622}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="1980" windowHeight="380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="94">
   <si>
     <t>academicachievement</t>
   </si>
@@ -309,6 +309,18 @@
   </si>
   <si>
     <t>Autonomy support</t>
+  </si>
+  <si>
+    <t>wellbeing</t>
+  </si>
+  <si>
+    <t>Wellbeing</t>
+  </si>
+  <si>
+    <t>mentalhealth</t>
+  </si>
+  <si>
+    <t>Mental health</t>
   </si>
 </sst>
 </file>
@@ -1219,9 +1231,33 @@
       <c r="E43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A44" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" t="s">
+        <v>93</v>
+      </c>
       <c r="E44" s="1"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" t="s">
+        <v>91</v>
+      </c>
       <c r="E45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">

--- a/data/topics_codebook.xlsx
+++ b/data/topics_codebook.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="654" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E63C9749-D00C-4EFE-ADA8-2469FDEB6622}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="1980" windowHeight="380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="variables" sheetId="2" r:id="rId1"/>
@@ -655,7 +655,7 @@
     <col min="2" max="2" width="18.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.453125" customWidth="1"/>
-    <col min="5" max="5" width="35.7265625" customWidth="1"/>
+    <col min="5" max="5" width="35.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.35">

--- a/data/topics_codebook.xlsx
+++ b/data/topics_codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="654" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E63C9749-D00C-4EFE-ADA8-2469FDEB6622}"/>
+  <xr:revisionPtr revIDLastSave="680" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{523D45BA-CC82-4B98-A7BD-873873DFDC51}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="110">
   <si>
     <t>academicachievement</t>
   </si>
@@ -321,6 +321,54 @@
   </si>
   <si>
     <t>Mental health</t>
+  </si>
+  <si>
+    <t>personalityfunctioning</t>
+  </si>
+  <si>
+    <t>Personality Functioning</t>
+  </si>
+  <si>
+    <t>methods</t>
+  </si>
+  <si>
+    <t>EMA</t>
+  </si>
+  <si>
+    <t>ema</t>
+  </si>
+  <si>
+    <t>Methods</t>
+  </si>
+  <si>
+    <t>esm</t>
+  </si>
+  <si>
+    <t>ESM</t>
+  </si>
+  <si>
+    <t>emotionregulation</t>
+  </si>
+  <si>
+    <t>Emotion Regulation</t>
+  </si>
+  <si>
+    <t>context</t>
+  </si>
+  <si>
+    <t>Context</t>
+  </si>
+  <si>
+    <t>skilluse</t>
+  </si>
+  <si>
+    <t>Skill use</t>
+  </si>
+  <si>
+    <t>metaanalysis</t>
+  </si>
+  <si>
+    <t>Meta analysis</t>
   </si>
 </sst>
 </file>
@@ -648,7 +696,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}">
-  <dimension ref="A1:AP117"/>
+  <dimension ref="A1:AP119"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" style="2" bestFit="1" customWidth="1"/>
@@ -1261,60 +1309,132 @@
       <c r="E45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" t="s">
+        <v>95</v>
+      </c>
       <c r="E46" s="1"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" t="s">
+        <v>102</v>
+      </c>
+      <c r="D47" t="s">
+        <v>103</v>
+      </c>
       <c r="E47" s="1"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="E48" s="1"/>
     </row>
-    <row r="49" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B49" t="s">
+        <v>99</v>
+      </c>
+      <c r="C49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" t="s">
+        <v>101</v>
+      </c>
       <c r="E49" s="1"/>
     </row>
-    <row r="50" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" t="s">
+        <v>98</v>
+      </c>
+      <c r="D50" t="s">
+        <v>97</v>
+      </c>
       <c r="E50" s="1"/>
     </row>
-    <row r="51" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" t="s">
+        <v>108</v>
+      </c>
+      <c r="D51" t="s">
+        <v>109</v>
+      </c>
       <c r="E51" s="1"/>
     </row>
-    <row r="52" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E52" s="1"/>
     </row>
-    <row r="53" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A53" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+      <c r="C53" t="s">
+        <v>106</v>
+      </c>
+      <c r="D53" t="s">
+        <v>107</v>
+      </c>
       <c r="E53" s="1"/>
     </row>
-    <row r="54" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E54" s="1"/>
     </row>
-    <row r="55" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E55" s="1"/>
     </row>
-    <row r="56" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E56" s="1"/>
     </row>
-    <row r="57" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E57" s="1"/>
     </row>
-    <row r="58" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E58" s="1"/>
     </row>
-    <row r="59" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E59" s="1"/>
     </row>
-    <row r="60" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E60" s="1"/>
     </row>
-    <row r="61" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E61" s="1"/>
     </row>
-    <row r="62" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E62" s="1"/>
     </row>
-    <row r="63" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E63" s="1"/>
     </row>
-    <row r="64" spans="5:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="E64" s="1"/>
     </row>
     <row r="65" spans="5:42" x14ac:dyDescent="0.35">
@@ -1328,51 +1448,49 @@
     </row>
     <row r="68" spans="5:42" x14ac:dyDescent="0.35">
       <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-      <c r="S68" s="1"/>
-      <c r="T68" s="1"/>
-      <c r="U68" s="1"/>
-      <c r="V68" s="1"/>
-      <c r="W68" s="1"/>
-      <c r="X68" s="1"/>
-      <c r="Y68" s="1"/>
-      <c r="Z68" s="1"/>
-      <c r="AA68" s="1"/>
-      <c r="AB68" s="1"/>
-      <c r="AC68" s="1"/>
-      <c r="AD68" s="1"/>
-      <c r="AE68" s="1"/>
-      <c r="AF68" s="1"/>
-      <c r="AG68" s="1"/>
-      <c r="AH68" s="1"/>
-      <c r="AI68" s="1"/>
-      <c r="AJ68" s="1"/>
-      <c r="AK68" s="1"/>
-      <c r="AL68" s="1"/>
-      <c r="AM68" s="1"/>
-      <c r="AN68" s="1"/>
-      <c r="AO68" s="1"/>
-      <c r="AP68" s="1"/>
     </row>
     <row r="69" spans="5:42" x14ac:dyDescent="0.35">
       <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
     </row>
     <row r="70" spans="5:42" x14ac:dyDescent="0.35">
       <c r="E70" s="1"/>
       <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+      <c r="M70" s="1"/>
+      <c r="N70" s="1"/>
+      <c r="O70" s="1"/>
+      <c r="P70" s="1"/>
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+      <c r="AB70" s="1"/>
+      <c r="AC70" s="1"/>
+      <c r="AD70" s="1"/>
+      <c r="AE70" s="1"/>
+      <c r="AF70" s="1"/>
+      <c r="AG70" s="1"/>
+      <c r="AH70" s="1"/>
+      <c r="AI70" s="1"/>
+      <c r="AJ70" s="1"/>
+      <c r="AK70" s="1"/>
+      <c r="AL70" s="1"/>
+      <c r="AM70" s="1"/>
+      <c r="AN70" s="1"/>
+      <c r="AO70" s="1"/>
+      <c r="AP70" s="1"/>
     </row>
     <row r="71" spans="5:42" x14ac:dyDescent="0.35">
       <c r="E71" s="1"/>
@@ -1384,13 +1502,21 @@
     </row>
     <row r="73" spans="5:42" x14ac:dyDescent="0.35">
       <c r="E73" s="1"/>
-    </row>
-    <row r="110" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="117" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="5:42" x14ac:dyDescent="0.35">
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="5:42" x14ac:dyDescent="0.35">
+      <c r="E75" s="1"/>
+    </row>
+    <row r="112" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="16" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:AP1" xr:uid="{471A8B26-530C-40CA-A676-99F1EAC2BADD}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:F181">
-    <sortCondition ref="A1:A181"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:F183">
+    <sortCondition ref="A1:A183"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
